--- a/6. Banc de test/Test_Bench_Graphite_Sensor.xlsx
+++ b/6. Banc de test/Test_Bench_Graphite_Sensor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Documents\Projet capteur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\INSA\4A\Projet MOSH\Git\2025-2026-4GP-Robinson-Podgorski\6. Banc de test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BEFE55-838A-4F49-BD1C-8CE7D19EC439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C825AB9C-ADCF-43AD-9856-2F53DA2579A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{26EDFF1A-5543-4014-A9E9-28F5123E8873}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26EDFF1A-5543-4014-A9E9-28F5123E8873}"/>
   </bookViews>
   <sheets>
     <sheet name="En tension" sheetId="1" r:id="rId1"/>
@@ -2525,7 +2525,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2873,7 +2873,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3186,7 +3186,7 @@
               <a:rPr lang="fr-FR" sz="1800" b="1" i="0" u="sng" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>Mesure de la variation relative de résistance en fonction de la déformation en tension</a:t>
+              <a:t>Mesure de la variation relative de résistance en fonction de la déformation en compression</a:t>
             </a:r>
             <a:endParaRPr lang="fr-FR">
               <a:effectLst/>
@@ -8517,16 +8517,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>442913</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>770573</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>172402</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8666,16 +8666,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>201500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>18916</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>285749</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>468200</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>106116</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8704,9 +8704,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8744,7 +8744,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8850,7 +8850,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8992,7 +8992,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9001,10 +9001,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6785BA91-B2E6-4BC9-96E2-4882BE9A1190}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9492,7 +9492,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D69588-0C06-417B-8E80-073DA47DB8A1}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
